--- a/excel/Indemo Rima.xlsx
+++ b/excel/Indemo Rima.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Indemo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.08.08\Indemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10C54576-12EC-4CE8-9ACF-AA39FAFA22DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD29E04-8E39-4AA4-AE5B-1D87BF23B256}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="33" r:id="rId1"/>
@@ -478,7 +478,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -560,15 +560,6 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -593,7 +584,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2545,41 +2536,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="37"/>
-      <c r="B1" s="38" t="s">
+      <c r="A1" s="34"/>
+      <c r="B1" s="35" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="34"/>
-      <c r="E1" s="35" t="s">
+      <c r="D1" s="31"/>
+      <c r="E1" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
-      <c r="I1" s="36"/>
-      <c r="K1" s="41" t="s">
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="33"/>
+      <c r="K1" s="38" t="s">
         <v>75</v>
       </c>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="35" t="s">
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="34" t="s">
+      <c r="P1" s="33"/>
+      <c r="Q1" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="34"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2" s="37"/>
-      <c r="B2" s="39"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="36"/>
       <c r="C2" s="20" t="s">
         <v>73</v>
       </c>
@@ -2628,7 +2619,7 @@
       <c r="S2" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="T2" s="32" t="s">
+      <c r="T2" s="20" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2706,7 +2697,7 @@
       </c>
       <c r="T3" s="6">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>1.3920126080513002</v>
+        <v>1.1574660420417782</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
@@ -3712,21 +3703,21 @@
       <c r="B1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3735,8 +3726,8 @@
       <c r="B2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -4336,21 +4327,21 @@
       <c r="B1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4359,8 +4350,8 @@
       <c r="B2" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -4960,21 +4951,21 @@
       <c r="B1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4983,8 +4974,8 @@
       <c r="B2" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -5584,21 +5575,21 @@
       <c r="B1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -5607,8 +5598,8 @@
       <c r="B2" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -6344,21 +6335,21 @@
       <c r="B1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -6367,8 +6358,8 @@
       <c r="B2" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -7079,21 +7070,21 @@
       <c r="B1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -7102,8 +7093,8 @@
       <c r="B2" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -7823,21 +7814,21 @@
       <c r="B1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -7846,8 +7837,8 @@
       <c r="B2" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -8567,21 +8558,21 @@
       <c r="B1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -8590,8 +8581,8 @@
       <c r="B2" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -9319,21 +9310,21 @@
       <c r="B1" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -9342,8 +9333,8 @@
       <c r="B2" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -10066,21 +10057,21 @@
       <c r="B1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -10089,8 +10080,8 @@
       <c r="B2" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -10739,10 +10730,10 @@
       <c r="H1" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="I1" s="33" t="s">
+      <c r="I1" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="K1" s="31" t="s">
+      <c r="K1" s="4" t="s">
         <v>78</v>
       </c>
     </row>
@@ -10773,7 +10764,7 @@
       </c>
       <c r="I2" s="6">
         <f ca="1">XIRR(K2:K200,A2:A200)</f>
-        <v>1.3920126080513002</v>
+        <v>1.1574660420417782</v>
       </c>
       <c r="K2" s="5">
         <f>B2*-1</f>
@@ -12193,7 +12184,7 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="25">
         <f ca="1">TODAY()</f>
-        <v>46236</v>
+        <v>46295</v>
       </c>
       <c r="B200" s="29"/>
       <c r="C200" s="29"/>
@@ -12230,21 +12221,21 @@
       <c r="B1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -12253,8 +12244,8 @@
       <c r="B2" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -12974,21 +12965,21 @@
       <c r="B1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -12997,8 +12988,8 @@
       <c r="B2" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -13718,21 +13709,21 @@
       <c r="B1" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -13741,8 +13732,8 @@
       <c r="B2" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -14492,21 +14483,21 @@
       <c r="B1" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -14515,8 +14506,8 @@
       <c r="B2" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -15266,21 +15257,21 @@
       <c r="B1" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -15289,8 +15280,8 @@
       <c r="B2" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -16040,21 +16031,21 @@
       <c r="B1" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -16063,8 +16054,8 @@
       <c r="B2" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -16814,21 +16805,21 @@
       <c r="B1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -16837,8 +16828,8 @@
       <c r="B2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -17588,21 +17579,21 @@
       <c r="B1" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -17611,8 +17602,8 @@
       <c r="B2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -18362,21 +18353,21 @@
       <c r="B1" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -18385,8 +18376,8 @@
       <c r="B2" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -19136,21 +19127,21 @@
       <c r="B1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -19159,8 +19150,8 @@
       <c r="B2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -19397,21 +19388,21 @@
       <c r="B1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -19420,8 +19411,8 @@
       <c r="B2" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -19663,21 +19654,21 @@
       <c r="B1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -19686,8 +19677,8 @@
       <c r="B2" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -20304,21 +20295,21 @@
       <c r="B1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -20327,8 +20318,8 @@
       <c r="B2" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -20921,21 +20912,21 @@
       <c r="B1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -20944,8 +20935,8 @@
       <c r="B2" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -21553,21 +21544,21 @@
       <c r="B1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -21576,8 +21567,8 @@
       <c r="B2" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
@@ -22176,21 +22167,21 @@
       <c r="B1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="44"/>
-      <c r="E1" s="38" t="s">
+      <c r="D1" s="41"/>
+      <c r="E1" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="36"/>
-      <c r="H1" s="35" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="40"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="40"/>
-      <c r="L1" s="36"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="33"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -22199,8 +22190,8 @@
       <c r="B2" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="39"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="36"/>
       <c r="F2" s="3" t="s">
         <v>32</v>
       </c>
